--- a/Lecture_4/tables/trade_2024.xlsx
+++ b/Lecture_4/tables/trade_2024.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice data" sheetId="1" r:id="R9f1594fd8b2f484e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice data" sheetId="1" r:id="R61a7c20e40a547fc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -318,7 +318,7 @@
         <x:v>year</x:v>
       </x:c>
       <x:c r="D1" s="5" t="str">
-        <x:v>export_milions_usd</x:v>
+        <x:v>export_millions_usd</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="25" customHeight="1">
